--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487990_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487990_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.6886</v>
+        <v>10.6481</v>
       </c>
       <c r="E2" t="n">
-        <v>10.605</v>
+        <v>10.4242</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0835</v>
+        <v>0.2239</v>
       </c>
       <c r="G2" t="n">
         <v>10.9408</v>
@@ -610,13 +610,13 @@
         <v>2.9733</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3029</v>
+        <v>-0.3433</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0038</v>
+        <v>-0.177</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3066</v>
+        <v>-0.1662</v>
       </c>
       <c r="V2" t="n">
         <v>-0.9405</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1386</v>
+        <v>6.727</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1549</v>
+        <v>5.6872</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9837</v>
+        <v>1.0399</v>
       </c>
       <c r="G3" t="n">
         <v>3.9517</v>
@@ -688,13 +688,13 @@
         <v>4.9556</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.174</v>
+        <v>-0.5855</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9873</v>
+        <v>-0.4551</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1866</v>
+        <v>-0.1305</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6036</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. GEA BECERRA</t>
+          <t>D. GARZON ALVAREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2649</v>
+        <v>2.0428</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6034</v>
+        <v>0.5622</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3385</v>
+        <v>1.4806</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.6782</v>
+        <v>-3.5004</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.3829</v>
+        <v>2.6408</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.2953</v>
+        <v>-6.1412</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0234</v>
+        <v>-0.2552</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4912</v>
+        <v>3.4982</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5145</v>
+        <v>-3.7534</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.6548</v>
+        <v>-3.2452</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.8741</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7806999999999999</v>
+        <v>-2.3879</v>
       </c>
       <c r="P5" t="n">
-        <v>1.784</v>
+        <v>4.3609</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R5" t="n">
-        <v>3.7662</v>
+        <v>5.352</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7449</v>
+        <v>-0.0248</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9877</v>
+        <v>-0.2687</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2428</v>
+        <v>0.2439</v>
       </c>
       <c r="V5" t="n">
-        <v>2.4142</v>
+        <v>1.2071</v>
       </c>
       <c r="W5" t="n">
-        <v>3.6213</v>
+        <v>2.0772</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2071</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. GARZON ALVAREZ</t>
+          <t>E. GEA BECERRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.097</v>
+        <v>1.3429</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3356</v>
+        <v>1.7095</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7614</v>
+        <v>-0.3666</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.5004</v>
+        <v>-2.6782</v>
       </c>
       <c r="H6" t="n">
-        <v>2.6408</v>
+        <v>-1.3829</v>
       </c>
       <c r="I6" t="n">
-        <v>-6.1412</v>
+        <v>-1.2953</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2552</v>
+        <v>-0.0234</v>
       </c>
       <c r="K6" t="n">
-        <v>3.4982</v>
+        <v>0.4912</v>
       </c>
       <c r="L6" t="n">
-        <v>-3.7534</v>
+        <v>-0.5145</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.2452</v>
+        <v>-2.6548</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-1.8741</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.3879</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>4.3609</v>
+        <v>1.784</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R6" t="n">
-        <v>5.352</v>
+        <v>3.7662</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0293</v>
+        <v>-0.1771</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4954</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5247000000000001</v>
+        <v>-0.2709</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2071</v>
+        <v>2.4142</v>
       </c>
       <c r="W6" t="n">
-        <v>2.0772</v>
+        <v>3.6213</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8701</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9738</v>
+        <v>0.882</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5358000000000001</v>
+        <v>-0.8414</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5096</v>
+        <v>1.7234</v>
       </c>
       <c r="G7" t="n">
         <v>-1.9231</v>
@@ -1000,13 +1000,13 @@
         <v>1.3876</v>
       </c>
       <c r="S7" t="n">
-        <v>1.6194</v>
+        <v>0.5276</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0552</v>
+        <v>-0.2505</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5643</v>
+        <v>0.7781</v>
       </c>
       <c r="V7" t="n">
         <v>1.8811</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8665</v>
+        <v>-0.4486</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8506</v>
+        <v>-0.545</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0159</v>
+        <v>0.0964</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4715</v>
@@ -1078,13 +1078,13 @@
         <v>0.5947</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9897</v>
+        <v>-0.5717</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5616</v>
+        <v>-0.256</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4281</v>
+        <v>-0.3158</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. LOPEZ SANCHEZ</t>
+          <t>J. MARTIN GONZALEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3811</v>
+        <v>-1.2258</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0733</v>
+        <v>-2.4735</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4543</v>
+        <v>1.2477</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1502</v>
+        <v>-1.2553</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.08069999999999999</v>
+        <v>0.9601</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0695</v>
+        <v>-2.2155</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3228</v>
+        <v>0.6523</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3228</v>
+        <v>2.4888</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-1.8365</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4731</v>
+        <v>-1.9076</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4036</v>
+        <v>-1.5286</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0695</v>
+        <v>-0.379</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.7662</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2309</v>
+        <v>-1.5583</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2496</v>
+        <v>-0.8065</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0187</v>
+        <v>-0.7518</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.1962</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.337</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.1408</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. OSORIO HERRERA</t>
+          <t>J. LOPEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,28 +1189,28 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6837</v>
+        <v>-1.353</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2294</v>
+        <v>0.0733</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4543</v>
+        <v>-1.4263</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.4529</v>
+        <v>-1.1502</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3834</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="I10" t="n">
         <v>-1.0695</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0202</v>
+        <v>0.3228</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0202</v>
+        <v>0.3228</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2309</v>
+        <v>-0.2028</v>
       </c>
       <c r="T10" t="n">
         <v>-0.2496</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. MARTIN GONZALEZ</t>
+          <t>M. PEREZ SARRABLO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8528</v>
+        <v>-1.362</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9039</v>
+        <v>-2.6914</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0511</v>
+        <v>1.3295</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.2553</v>
+        <v>-1.5342</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9601</v>
+        <v>-0.5394</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.2155</v>
+        <v>-0.9949</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6523</v>
+        <v>-0.2202</v>
       </c>
       <c r="K11" t="n">
-        <v>2.4888</v>
+        <v>-0.1476</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.8365</v>
+        <v>-0.0726</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9076</v>
+        <v>-1.3141</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5286</v>
+        <v>-0.3918</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.379</v>
+        <v>-0.9223</v>
       </c>
       <c r="P11" t="n">
-        <v>1.784</v>
+        <v>1.3876</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.9822</v>
       </c>
       <c r="R11" t="n">
-        <v>3.7662</v>
+        <v>3.3698</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.1852</v>
+        <v>-1.2857</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2369</v>
+        <v>-0.489</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9483</v>
+        <v>-0.7967</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1962</v>
+        <v>0.0704</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.337</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1408</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. GARCIA GUERRERO</t>
+          <t>A. OSORIO HERRERA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,31 +1345,31 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.9463</v>
+        <v>-1.6557</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9085</v>
+        <v>-0.2294</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0377</v>
+        <v>-1.4263</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.132</v>
+        <v>-1.4529</v>
       </c>
       <c r="H12" t="n">
         <v>-0.3834</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.7486</v>
+        <v>-1.0695</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.659</v>
+        <v>0.0202</v>
       </c>
       <c r="K12" t="n">
         <v>0.0202</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6791</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>-1.4731</v>
@@ -1381,22 +1381,22 @@
         <v>-1.0695</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0125</v>
+        <v>-0.2028</v>
       </c>
       <c r="T12" t="n">
         <v>-0.2496</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2371</v>
+        <v>0.0468</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. PEREZ SARRABLO</t>
+          <t>A. GARCIA GUERRERO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.2082</v>
+        <v>-2.0586</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.2008</v>
+        <v>-0.9085</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9925</v>
+        <v>-1.15</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.5342</v>
+        <v>-2.132</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5394</v>
+        <v>-0.3834</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9949</v>
+        <v>-1.7486</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2202</v>
+        <v>-0.659</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1476</v>
+        <v>0.0202</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.0726</v>
+        <v>-0.6791</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.3141</v>
+        <v>-1.4731</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3918</v>
+        <v>-0.4036</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9223</v>
+        <v>-1.0695</v>
       </c>
       <c r="P13" t="n">
-        <v>1.3876</v>
+        <v>0.1982</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.3698</v>
+        <v>0.1982</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.132</v>
+        <v>-0.1248</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9984</v>
+        <v>-0.2496</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1336</v>
+        <v>0.1248</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0704</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0704</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.294</v>
+        <v>-3.9851</v>
       </c>
       <c r="E14" t="n">
         <v>-4.529</v>
       </c>
       <c r="F14" t="n">
-        <v>0.235</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>-1.8827</v>
@@ -1546,13 +1546,13 @@
         <v>2.3787</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8255</v>
+        <v>-0.5167</v>
       </c>
       <c r="T14" t="n">
         <v>-0.2568</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5687</v>
+        <v>-0.2598</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,16 +1579,16 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>11.3463</v>
+        <v>11.97</v>
       </c>
       <c r="E15" t="n">
-        <v>8.030200000000001</v>
+        <v>8.654199999999999</v>
       </c>
       <c r="F15" t="n">
         <v>3.3161</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6719999999999993</v>
+        <v>-0.6720000000000008</v>
       </c>
       <c r="H15" t="n">
         <v>11.4667</v>
@@ -1597,13 +1597,13 @@
         <v>-12.1388</v>
       </c>
       <c r="J15" t="n">
-        <v>19.1634</v>
+        <v>19.16340000000001</v>
       </c>
       <c r="K15" t="n">
         <v>18.7411</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4224999999999994</v>
+        <v>0.4225000000000003</v>
       </c>
       <c r="M15" t="n">
         <v>-19.8357</v>
@@ -1624,19 +1624,19 @@
         <v>28.7423</v>
       </c>
       <c r="S15" t="n">
-        <v>-5.69</v>
+        <v>-5.0659</v>
       </c>
       <c r="T15" t="n">
-        <v>-4.2385</v>
+        <v>-3.6146</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.4512</v>
+        <v>-1.4513</v>
       </c>
       <c r="V15" t="n">
         <v>3.8325</v>
       </c>
       <c r="W15" t="n">
-        <v>7.971900000000002</v>
+        <v>7.971900000000001</v>
       </c>
       <c r="X15" t="n">
         <v>-4.1394</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.3289</v>
+        <v>3.304</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8047</v>
+        <v>3.4991</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4759</v>
+        <v>-0.1951</v>
       </c>
       <c r="G16" t="n">
         <v>3.6922</v>
@@ -1702,13 +1702,13 @@
         <v>0.3964</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2313</v>
+        <v>0.2065</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3158</v>
+        <v>0.0102</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.08450000000000001</v>
+        <v>0.1963</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5762</v>
+        <v>1.2131</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0968</v>
+        <v>1.4856</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5206</v>
+        <v>-0.2725</v>
       </c>
       <c r="G17" t="n">
         <v>0.3689</v>
@@ -1780,13 +1780,13 @@
         <v>1.5858</v>
       </c>
       <c r="S17" t="n">
-        <v>1.5176</v>
+        <v>1.1545</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2373</v>
+        <v>0.626</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2803</v>
+        <v>0.5285</v>
       </c>
       <c r="V17" t="n">
         <v>1.4737</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.451</v>
+        <v>0.5601</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7266</v>
+        <v>-1.421</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1776</v>
+        <v>1.9811</v>
       </c>
       <c r="G18" t="n">
         <v>0.439</v>
@@ -1858,13 +1858,13 @@
         <v>1.1893</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8048999999999999</v>
+        <v>0.914</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3523</v>
+        <v>-0.0467</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1572</v>
+        <v>0.9607</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. OLIVER ARENAS</t>
+          <t>M. VIGO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1358</v>
+        <v>0.3476</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1.7339</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1358</v>
+        <v>-1.3863</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1358</v>
+        <v>0.5699</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-2.122</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1358</v>
+        <v>2.6919</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>3.4767</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1.0907</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.386</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1358</v>
+        <v>-2.9069</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-3.2127</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1358</v>
+        <v>0.3059</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.3698</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.5769</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.3745</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.0429</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.4174</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.1962</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.6698</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. PEREIRA FERNANDES</t>
+          <t>B. OLIVER ARENAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.058</v>
+        <v>0.1358</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5203</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5783</v>
+        <v>0.1358</v>
       </c>
       <c r="G20" t="n">
-        <v>0.596</v>
+        <v>0.1358</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7987</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2027</v>
+        <v>0.1358</v>
       </c>
       <c r="J20" t="n">
-        <v>2.9054</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>3.0065</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1011</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.3094</v>
+        <v>0.1358</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.2078</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1016</v>
+        <v>0.1358</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.784</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3549</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3306</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.0243</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.8107</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.0772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. VIGO RODRIGUEZ</t>
+          <t>R. PEREIRA FERNANDES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1637</v>
+        <v>-0.5144</v>
       </c>
       <c r="E21" t="n">
-        <v>1.8358</v>
+        <v>1.3166</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9994</v>
+        <v>-1.831</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5699</v>
+        <v>0.596</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.122</v>
+        <v>0.7987</v>
       </c>
       <c r="I21" t="n">
-        <v>2.6919</v>
+        <v>-0.2027</v>
       </c>
       <c r="J21" t="n">
-        <v>3.4767</v>
+        <v>2.9054</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0907</v>
+        <v>3.0065</v>
       </c>
       <c r="L21" t="n">
-        <v>2.386</v>
+        <v>-0.1011</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.9069</v>
+        <v>-2.3094</v>
       </c>
       <c r="N21" t="n">
-        <v>-3.2127</v>
+        <v>-2.2078</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3059</v>
+        <v>-0.1016</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.7929</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.3698</v>
+        <v>-1.9822</v>
       </c>
       <c r="R21" t="n">
-        <v>2.5769</v>
+        <v>1.784</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1368</v>
+        <v>0.8985</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0589</v>
+        <v>0.1269</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1958</v>
+        <v>0.7716</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1962</v>
+        <v>-1.8107</v>
       </c>
       <c r="W21" t="n">
-        <v>1.6698</v>
+        <v>0.2666</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4737</v>
+        <v>-2.0772</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8658</v>
+        <v>-3.5223</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0004</v>
+        <v>-3.2873</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1346</v>
+        <v>-0.235</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1961</v>
@@ -2170,13 +2170,13 @@
         <v>2.7751</v>
       </c>
       <c r="S22" t="n">
-        <v>1.1937</v>
+        <v>1.5372</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4109</v>
+        <v>0.3022</v>
       </c>
       <c r="U22" t="n">
-        <v>1.6046</v>
+        <v>1.235</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2775</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.8454</v>
+        <v>-5.5515</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.1824</v>
+        <v>-4.0806</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6629</v>
+        <v>-1.471</v>
       </c>
       <c r="G23" t="n">
         <v>-2.6738</v>
@@ -2248,13 +2248,13 @@
         <v>2.3787</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4559</v>
+        <v>0.7498</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4444</v>
+        <v>0.5462</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0116</v>
+        <v>0.2036</v>
       </c>
       <c r="V23" t="n">
         <v>0.337</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.9053</v>
+        <v>-6.6396</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6642</v>
+        <v>-2.5624</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.2411</v>
+        <v>-4.0772</v>
       </c>
       <c r="G24" t="n">
         <v>-0.2598</v>
@@ -2326,13 +2326,13 @@
         <v>2.1805</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2683</v>
+        <v>0.5341</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1724</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4407</v>
+        <v>0.6046</v>
       </c>
       <c r="V24" t="n">
         <v>-2.7512</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-11.3463</v>
+        <v>-10.6672</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.316</v>
+        <v>-3.316099999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-8.030200000000001</v>
+        <v>-7.3512</v>
       </c>
       <c r="G25" t="n">
         <v>0.6720999999999997</v>
@@ -2392,7 +2392,7 @@
         <v>-18.7409</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.4226000000000003</v>
+        <v>-0.4226000000000001</v>
       </c>
       <c r="P25" t="n">
         <v>-13.8757</v>
@@ -2404,13 +2404,13 @@
         <v>14.8667</v>
       </c>
       <c r="S25" t="n">
-        <v>5.6898</v>
+        <v>6.3691</v>
       </c>
       <c r="T25" t="n">
         <v>1.4514</v>
       </c>
       <c r="U25" t="n">
-        <v>4.2384</v>
+        <v>4.9177</v>
       </c>
       <c r="V25" t="n">
         <v>-3.8325</v>
